--- a/main/ig/StructureDefinition-eclaire-group.xlsx
+++ b/main/ig/StructureDefinition-eclaire-group.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-25T15:44:45+00:00</t>
+    <t>2025-11-27T10:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -644,7 +644,7 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -852,7 +852,7 @@
     <t>Group.member.entity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|Medication|Substance|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Medication|4.0.1|Substance|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1220,7 +1220,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.5234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.2265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3643,7 +3643,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>226</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>242</v>
       </c>
@@ -4951,12 +4951,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL34">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-eclaire-group.xlsx
+++ b/main/ig/StructureDefinition-eclaire-group.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T10:20:46+00:00</t>
+    <t>2025-11-27T15:06:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
